--- a/example_output/versions/spreadsheets/indirect_costs_final.xlsx
+++ b/example_output/versions/spreadsheets/indirect_costs_final.xlsx
@@ -457,7 +457,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>202301</v>
+        <v>202401</v>
       </c>
       <c r="B2" t="n">
         <v>1</v>
@@ -474,7 +474,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>202302</v>
+        <v>202402</v>
       </c>
       <c r="B3" t="n">
         <v>1</v>
@@ -491,7 +491,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>202303</v>
+        <v>202403</v>
       </c>
       <c r="B4" t="n">
         <v>1</v>
@@ -508,7 +508,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>202304</v>
+        <v>202404</v>
       </c>
       <c r="B5" t="n">
         <v>1</v>
@@ -525,7 +525,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>202305</v>
+        <v>202405</v>
       </c>
       <c r="B6" t="n">
         <v>1</v>
@@ -542,7 +542,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>202306</v>
+        <v>202406</v>
       </c>
       <c r="B7" t="n">
         <v>1</v>
@@ -559,7 +559,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>202307</v>
+        <v>202407</v>
       </c>
       <c r="B8" t="n">
         <v>1</v>
@@ -576,7 +576,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>202308</v>
+        <v>202408</v>
       </c>
       <c r="B9" t="n">
         <v>1</v>
@@ -593,7 +593,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>202309</v>
+        <v>202409</v>
       </c>
       <c r="B10" t="n">
         <v>1</v>
@@ -610,7 +610,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>202310</v>
+        <v>202410</v>
       </c>
       <c r="B11" t="n">
         <v>1</v>

--- a/example_output/versions/spreadsheets/indirect_costs_final.xlsx
+++ b/example_output/versions/spreadsheets/indirect_costs_final.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -625,6 +625,23 @@
         <v>390229.89</v>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>202411</v>
+      </c>
+      <c r="B12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" t="n">
+        <v>262180.98</v>
+      </c>
+      <c r="D12" t="n">
+        <v>59029.8</v>
+      </c>
+      <c r="E12" t="n">
+        <v>321210.78</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
